--- a/Evaluaciones/Proyectos/AvanceGrupos.xlsx
+++ b/Evaluaciones/Proyectos/AvanceGrupos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EGCC\PortableGit\UPN_2026_2_DAS_26084\Evaluaciones\Proyectos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65DF78DF-99FC-4373-8AA4-7452F07D7E94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E722309F-644A-4BEF-98A1-3F90C967CBC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="5">
   <si>
     <t>GRUPO</t>
   </si>
@@ -40,6 +40,9 @@
   </si>
   <si>
     <t>P</t>
+  </si>
+  <si>
+    <t>01.OCT</t>
   </si>
 </sst>
 </file>
@@ -418,7 +421,7 @@
   <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="9.140625" style="1"/>
+    <col min="1" max="4" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -431,7 +434,9 @@
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3"/>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
@@ -449,7 +454,7 @@
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
-      <c r="D2" s="5"/>
+      <c r="D2" s="4"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
@@ -467,7 +472,7 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
+      <c r="D3" s="4"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -485,7 +490,7 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
-      <c r="D4" s="5"/>
+      <c r="D4" s="4"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
@@ -505,7 +510,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
+      <c r="D5" s="4"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
@@ -525,7 +530,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="4"/>
-      <c r="D6" s="5"/>
+      <c r="D6" s="4"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -545,7 +550,9 @@
       <c r="C7" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="5"/>
+      <c r="D7" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
@@ -563,7 +570,7 @@
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
-      <c r="D8" s="5"/>
+      <c r="D8" s="4"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
@@ -583,7 +590,7 @@
       <c r="C9" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="5"/>
+      <c r="D9" s="4"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
